--- a/Data_thang/Thang_04_2026.xlsx
+++ b/Data_thang/Thang_04_2026.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J264"/>
+  <dimension ref="A1:J382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12609,6 +12609,5253 @@
       <c r="I264" t="inlineStr">
         <is>
           <t>BHHT My Lân</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>263003050</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-03-30 15:10:00</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>LA-Nk Kim Oanh</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Muội</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:34-35, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>2</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>260903064-3</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:34:00</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Bà Năm</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Tháo lắp Răng Newace, Cosmo (Nhật ) (R:HTren, - SL: 14)</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>14</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Thử R lại - CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>263003047</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-03-30 11:25:00</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>La Thị Ngọc Trinh</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:33-37, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>5</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>HT CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>263003046</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-03-30 11:25:00</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Nguyễn Trần Xuân Nhuỵ</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Răng sứ Zir- Diamond (R:31-41,32-33,42-43, - SL: 6)</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>6</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>HT CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>263003038</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:05:00</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>LA-Nk Tâm Đức</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Hai</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:26-27, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>2</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>263003037</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:03:00</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>LA-Nk Tâm Đức</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Vân</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:36, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>1</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>263003036</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:02:00</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Ngô Nguyễn Thuỳ Lâm</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:36, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>1</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>263003035</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-03-30 09:58:00</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Ngọc Quý</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:44-46, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>3</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>263003044</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:55:00</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Đoàn T Kim Liên</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Khung kim loại (R:HDuoi, - SL: 1); 
+Lên gối sáp (R:HDuoi, - SL: 1); 
+Răng sứ kim loại thường (R:13-15, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>5</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>HT
+Đã tách giấy</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>261903064-3</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-03-31 20:03:00</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>SG-Nk  Hậu - Bình Chánh</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Cẩm Vân</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:13-22, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>5</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Đắp hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>263103055</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:55:00</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>SG-Nk  Hậu - Bình Chánh</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Loan</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:45-46, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>2</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>263103050</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:32:00</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>LA-Nk Tố Oanh</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Nguyễn Ngọc Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Full sứ Cercon HT (R:46, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>1</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>262803052-1</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:16:00</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>LA-Nk Tố Oanh</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Thái Thị Đẹt</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:13-15, - SL: 3); 
+Veneer sứ Titanium (Cut Back) (R:12, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>4</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Đắp hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>262103050-4</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:12:00</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:00:00</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Chú Liên (38337)</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Tháo lắp Răng Justi (Mỹ) (R:HTren, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>262203043-2</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:27:00</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Hợp</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:25-27, - SL: 3); 
+Răng sứ kim loại thường (R:32-38,31-42,43-44, - SL: 12)</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>15</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>LL+LT - GỬI CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>263103043</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:21:00</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Võ Thành An</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:26-27, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>2</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>HT - GỬI CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>263103037</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:48:00</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Bùi Thị Rất</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Lên gối sáp (R:HTren,HDuoi, - SL: 2); 
+Răng sứ kim loại thường (R:11-24,42-44, - SL: 8)</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>10</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>263103029</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:18:00</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Trần Tấn Khanh</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Veneer sứ Ziconia (Cut Back) (R:12-21, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>3</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>263103028</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:15:00</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Thu Thảo</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:23-25,41, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>4</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>263103027</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:40:00</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:00:00</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Chị Thuỷ (40795)</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Cùi giả (R:24, - SL: 1); 
+Răng Tạm (R:24-27, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>263103012</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:18:00</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>TN-Nk  NHO</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>A Huy</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Răng sứ Zir- Diamond (R:13, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>1</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>263003052</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-03-30 16:00:00</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:00:00</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>LA-Nk Tố Oanh</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Võ Văn Cả</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:46-47, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
+        <v>2</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>263103018</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:50:00</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>SG-Nk  Anh Khôi</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Khung kim loại (R:HDuoi, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>1</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Thử khung. có book grab sớm càng tốt</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>263103051</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-03-31 17:35:00</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Ái</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Phan Thị Minh Thảo</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:23-26, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
+        <v>4</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Thử thô</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>262703057-2</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-03-31 17:35:00</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Ái</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Cao Thị Hồng Phượng</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Cùi giả (R:24,25, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
+        <v>2</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>LT Hạnh Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>262703057-1</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:50:00</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Ái</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Cao Thị Hồng Phượng</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:43-47,34-35, - SL: 7)</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
+        <v>7</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>NB hoàn tất Trường Trân</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>262703009-1</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:29:00</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>TV-Nk Đức Hiền</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Dương Dan</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:13-24, - SL: 7)</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
+        <v>7</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Sửa Trang Hỷ
+GẤP KHÔNG HẸN</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>252405030-3</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:45:00</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>AG-Nk Hồng Thọ</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Hứa T Kim Tuyền</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12-13,11,21,22, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
+        <v>5</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>BHHT Phong Hạnh Sĩ Hồng Hỷ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>263103034</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:39:00</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>AG-Nk Hồng Thọ</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Trần Văn Lộc</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:22-24,14-16, - SL: 6)</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>6</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>263103033</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:34:00</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>AG-Nk Hồng Thọ</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Nguyễn T Thoa</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:44-47, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
+        <v>4</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>263103032</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:29:00</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>AG-Nk Hồng Thọ</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Bùi Văn Vẹn</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12-15, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H295" t="n">
+        <v>4</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>263103011</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:13:00</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Vũ - BC</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Luân</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:16-17,26-27, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
+        <v>4</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>HT 
+GK of NK</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>263103004</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-03-31 07:42:00</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>AG-Nk Thủy Tùng</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Soekhum</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Full/ mão kim loại sứ (R:27, - SL: 1); 
+Răng sứ kim loại thường (R:13-26, - SL: 9)</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>10</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>263103003</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-03-31 07:39:00</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>AG-Nk Thủy Tùng</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Thuý</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Cùi giả (R:11, - SL: 1); 
+Răng Tạm (R:11, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>2</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Đã tách giấy</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>262903047-1</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:25:00</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>SG-Nk  Anh Khôi</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Chúc</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:15-22,33-35, - SL: 10)</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
+        <v>10</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>HT Không có chuyến thì book grab</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>262503006-1</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:22:00</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>AG-Nk Thủy Tùng</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Huyền</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:43-45, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H300" t="n">
+        <v>3</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Sửa Vy Tuấn</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>260903019-2</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:22:00</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>KG-Nk Thanh Song</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Anh Tường</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại đắp sứ VITA (R:16-23,24-25, - SL: 10); 
+Răng sứ kim loại thường (R:34-37,44-45, - SL: 6)</t>
+        </is>
+      </c>
+      <c r="H301" t="n">
+        <v>16</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>LLHT + Sửa. GỬI KG
+Trường - Trường</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>263003045</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-03-30 10:28:00</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>KG-Nk Thanh Song</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Chức</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:17, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>1</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Hoàn tất. GỬI KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>260302035-1</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:09:00</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>DT-Nk Sa Đéc</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Hoàng Thuận</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12-22, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>4</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>263103021</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:04:00</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>AG-Nk Nguyễn Gia</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Huỳnh Thị Ngọc An</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:24-27, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>4</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>263103020</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:00:00</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>AG-Nk Nguyễn Gia</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Lâm Thị Kim Em</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:25, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H305" t="n">
+        <v>1</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>262303028-1</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:57:00</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>TV-Nk  Bs Liêm</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Trần Thị Thu Hồng</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Full Sứ Ziconia (R:45, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>1</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>LTHT My Lân</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>263103019</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:52:00</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>DT-Nk Sa Đéc</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Kiều Tâm</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:13-14,44, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>3</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>262003023-2</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:46:00</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>AG-Nk An Châu</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Phạm Hữu Tài</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:45-46, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>2</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>LLHT My Hữu</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>263103025</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:23:00</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>AG-Nk An Châu</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Trần Thị Mỹ Dung</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:15, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>1</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>263103024</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:20:00</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>AG-Nk An Châu</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Ngô Thị Thuỳ Oanh</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:11-21, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>2</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>263103023</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:13:00</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>AG-Nk An Châu</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Hạnh</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11-24, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>5</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>20110018-2</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:32:00</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Trần Thị Liên (Liền)</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:21, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>1</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>BHHT Vạn Thảo Thảo Trường Lân</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>263103002</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-03-31 07:36:00</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Nguyễn Thanh Vàng</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:33-42, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>5</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>263103001</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-03-31 07:33:00</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Trần Bích Vân</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:11, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H314" t="n">
+        <v>1</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>262703038-1</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:14:00</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>DL-Nk BS Quyên</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Hải</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Full Sứ Ziconia (R:27, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>1</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>LLHT My Lân</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>263103010</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:10:00</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>AG-Nk Mai Thảo</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Nuôi</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:32-34, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H316" t="n">
+        <v>3</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>263103008</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:06:00</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>DL-Nk Đức Trọng</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Nhung</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Veneer sứ Ziconia (Cut Back) (R:11,12,21, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H317" t="n">
+        <v>3</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>263103007</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-03-31 07:57:00</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>AG-Nk Quốc Huy</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Chú 8</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:35-47, - SL: 12)</t>
+        </is>
+      </c>
+      <c r="H318" t="n">
+        <v>12</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>263103006</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-03-31 07:49:00</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>AG-Nk Quốc Huy</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Con Chú Hoa</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:22, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H319" t="n">
+        <v>1</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>263103017</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:49:00</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>TV-Nk Sài Gòn ( Bs Bảo)</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Đặng Thị Sinh</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:26, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H320" t="n">
+        <v>1</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>263103016</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:45:00</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>NT-Nk BS Thuận</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Thu Thuỷ</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Răng sứ Cercon HT (R:12-13, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H321" t="n">
+        <v>2</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>263103015</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:33:00</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>NT-Nk BS Thuận</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Nguyễn Cảnh</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:42-44, - SL: 3); 
+Tháo lắp Răng Excellent (Denlay) (R:HTren,HDuoi, - SL: 16)</t>
+        </is>
+      </c>
+      <c r="H322" t="n">
+        <v>19</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>HT 
+10H (01/04) xong sứ thô gửi anh Bửu 
+15H (01/04) anh Bửu giao lại NBHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>262303024-2</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:32:00</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>NT-Nk BS Thuận</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Đình Thiên</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Khung kim loại (R:HDuoi, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H323" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>263103014</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:28:00</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Thành Thái</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Full Zirconia HT (R:24,34, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H324" t="n">
+        <v>2</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>262603019-1</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:24:00</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Hiệp</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11-21, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H325" t="n">
+        <v>2</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>262803008-1</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:18:00</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Huỳnh Thanh Hiếu</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Móc nhựa dẻo (R:HTren, - SL: 2); 
+Tháo lắp Răng Kenson, Vitadent  (VN) (R:HTren, - SL: 9)</t>
+        </is>
+      </c>
+      <c r="H326" t="n">
+        <v>11</v>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>EN GK of Labo</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>262603052-1</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:00:00</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Anh Phát (47164)</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:15, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H327" t="n">
+        <v>1</v>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>262803036-1</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:48:00</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Chị Chi (47071)</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:14-24,25-27, - SL: 11)</t>
+        </is>
+      </c>
+      <c r="H328" t="n">
+        <v>11</v>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Đắp hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>262803049-1</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:30:00</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>C Trinh (47289)</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:16, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H329" t="n">
+        <v>1</v>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>263103048</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:22:00</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Cô Lâm (47305)</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Răng Tạm (R:17-27, - SL: 14)</t>
+        </is>
+      </c>
+      <c r="H330" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>261503037-1</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:18:00</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Anh Bình (47159)</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:45-47, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H331" t="n">
+        <v>3</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Sửa Hồng Thư</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>262903031-1</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:13:00</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Anh Chung (47041)</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:35-37, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H332" t="n">
+        <v>3</v>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Đắp hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>263103026</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-03-31 09:38:00</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:00:00</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Bổn (35145)</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Răng Tạm (R:11, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H333" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>262803031-1</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:02:00</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:16-27, - SL: 13)</t>
+        </is>
+      </c>
+      <c r="H334" t="n">
+        <v>13</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>263103040</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:00:00</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Lữ Thị Thanh Thanh</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:16, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H335" t="n">
+        <v>1</v>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>263103039</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:58:00</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Nguyễn T Niềm</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:15, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H336" t="n">
+        <v>1</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>263103054</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:49:00</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>SG-Nk  Hậu - Bình Chánh</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Hồng</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Veneer sứ Zir-Diamond (Cut-Back) (R:15, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H337" t="n">
+        <v>1</v>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>263103056</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-03-31 19:57:00</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>SG-Nk  Hậu - Bình Chánh</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:25, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H338" t="n">
+        <v>1</v>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>263103046</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:30:00</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:30:00</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>SG-Nk Như Lạc</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Trung</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>In Mẫu Toàn Hàm (R:HDuoi, - SL: 1); 
+Răng sứ Zircornia (R:33-42,43, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H339" t="n">
+        <v>6</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>263103044</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:39:00</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:00:00</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>SG-Nk Mỹ Á</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>A.Phong</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Răng Tạm (R:14-24, - SL: 8)</t>
+        </is>
+      </c>
+      <c r="H340" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>262803053-1</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:35:00</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:00:00</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>SG-Nk Việt Xuân</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Thu Huỳnh</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:17, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H341" t="n">
+        <v>1</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Sửa Vy Trân</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>263103049</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:30:00</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:00:00</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:00:00</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>SG-Nk Mỹ Á</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Cô Lương</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:27, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H342" t="n">
+        <v>1</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>240705054-5</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:50:00</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:00:00</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Anh Wong Ken (39007)</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Răng sứ Chrome - Cobalt (R:22-27, - SL: 6)</t>
+        </is>
+      </c>
+      <c r="H343" t="n">
+        <v>6</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Sửa Vy An
+GK của NK</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>263103053</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:54:00</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:00:00</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>LA-Nk Tân Bửu</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Nguyễn Phát Đạt</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Full/ mão kim loại sứ (R:37, - SL: 1); 
+Răng sứ kim loại thường (R:32-36, - SL: 5); 
+Veneer sứ kim loại thường (Cut Back) (R:13-25, - SL: 8)</t>
+        </is>
+      </c>
+      <c r="H344" t="n">
+        <v>14</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>263103052</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-03-31 18:47:00</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:00:00</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>LA-Nk Tân Bửu</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Ngọc Sương</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Khung kim loại (R:HTren, - SL: 1); 
+Tháo lắp Răng Newace, Cosmo (Nhật ) (R:HTren, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H345" t="n">
+        <v>2</v>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Thử khung Thử R</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>263103041</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:13:00</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:00:00</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>LA-Nk Tâm Đức</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Hạnh</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Nền hàm Bio hai bên (R:HTren, - SL: 1); 
+Tháo lắp Răng  Ortolux (Ngoại) (R:HTren, - SL: 7)</t>
+        </is>
+      </c>
+      <c r="H346" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>263103031</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:30:00</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:00:00</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>LA-Nk Tâm Đức</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Thanh Kiều</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:34-35, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H347" t="n">
+        <v>2</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>263103030</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:30:00</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:00:00</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>LA-Nk Tâm Đức</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Đặng Văn Huynh</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:12, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H348" t="n">
+        <v>1</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>263003051</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2026-03-30 15:15:00</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:00:00</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>SG-Nk  Anh Khôi</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:36, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H349" t="n">
+        <v>1</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>263103042</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2026-03-31 11:35:00</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Cô Mai (47231)</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Răng sứ Cercon HT (R:12-16, - SL: 5); 
+Veneer sứ Cercon HT (Cut-Back) (R:11-21, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H350" t="n">
+        <v>7</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>260104017</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:39:00</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:00:00</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>SG-Nk Như Lạc</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Triệu Vĩ Khang</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>In Mẫu Toàn Hàm (R:HTren,HDuoi, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H351" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>241910001-2</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:39:00</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Tín</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:24-25, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H352" t="n">
+        <v>2</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Sửa Vy - Lân</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>240705039-14</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:48:00</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Thầy Đạt</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Veneer sứ kim loại thường (Cut Back) (R:17-27, - SL: 14)</t>
+        </is>
+      </c>
+      <c r="H353" t="n">
+        <v>14</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Sửa Trang -Tuấn</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>260104022</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:56:00</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Ái Chiêm</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Khay cá nhân (R:HTren,HDuoi, - SL: 2); 
+Tháo lắp Răng Sứ Vita (R:HTren,HDuoi, - SL: 0)</t>
+        </is>
+      </c>
+      <c r="H354" t="n">
+        <v>2</v>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Thử răng</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>262403023-2</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:34:00</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>DT-Nk Sa Đéc</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Thanh Thiện</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12-22, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H355" t="n">
+        <v>4</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Sửa Hồng - Hữu</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>260104016</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:32:00</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>DT-Nk Sa Đéc</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Thuý An</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Cùi giả (R:47, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H356" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>262103019-2</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:30:00</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>NT-Nk BS Thuận</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Bảo Ân</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:14-24, - SL: 8)</t>
+        </is>
+      </c>
+      <c r="H357" t="n">
+        <v>8</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Sửa Hồng - Ko tên</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>260104015</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:22:00</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>DT-Nk Sa Đéc</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Thành Chiến</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Cùi giả (R:11,21, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H358" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>262903010-1</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:58:00</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Phan Thanh Hùng</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:25-27,33-41,34-37,42-43, - SL: 12)</t>
+        </is>
+      </c>
+      <c r="H359" t="n">
+        <v>12</v>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Sửa My - Tuấn</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>252609027-1</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:43:00</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:30:00</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Nga</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:33-37, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H360" t="n">
+        <v>5</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Sửa Vy - Hữu</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>260104018</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:46:00</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>CT-NK Thanh Vũ II-TN</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Anh Kiệt</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Cùi giả (R:22, - SL: 1); 
+Răng sứ kim loại thường (R:21-22, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H361" t="n">
+        <v>3</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>260104003</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:46:00</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:00:00</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>TV-Nk Đức Hiền</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>E Uyên</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:45, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H362" t="n">
+        <v>1</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>260104002</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:50:00</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:00:00</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>TV-Nk Đức Hiền</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>E Hương</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:11-12, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H363" t="n">
+        <v>2</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>260104009</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:13:00</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:00:00</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>KG-Nk Sài Gòn</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Kim Thoa (642)</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:21, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H364" t="n">
+        <v>1</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>260104007</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:11:00</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:00:00</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>KG-Nk Sài Gòn</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Tạ Đức Vỹ (1504)</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Full Sứ Zolid (R:27, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H365" t="n">
+        <v>1</v>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>260104006</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:06:00</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:00:00</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Vũ - BC</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Nguyễn Thanh Sang</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12-22, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H366" t="n">
+        <v>4</v>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Hoàn tất. GK CỦA NK</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>263003004-1</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:02:00</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Huỳnh Văn Ngọc</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:44-45, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H367" t="n">
+        <v>2</v>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>260104008</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:11:00</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>AG-Nk Lê Hùng</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Thọ</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H368" t="n">
+        <v>1</v>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>260104001</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:38:00</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>AG-Nk Minh Đức</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:11-21, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H369" t="n">
+        <v>2</v>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>260104005</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:49:00</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>TV-Nk BS Hoài</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Bằng</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:12-21, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H370" t="n">
+        <v>3</v>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>260104004</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2026-04-01 07:49:00</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>TV-Nk BS Hoài</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Sen</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Răng sứ Zolid (R:22, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H371" t="n">
+        <v>1</v>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>262703023-1</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:34:00</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>DT-Nk Sa Đéc</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Tuấn Quốc</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:16, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H372" t="n">
+        <v>1</v>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>260104021</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:53:00</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>AG-Nk Hiệp Thành</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Cùi giả (R:12, - SL: 1); 
+Răng sứ kim loại thường (R:12, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H373" t="n">
+        <v>2</v>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>260104020</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:51:00</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>NT-Nk BS Thuận</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Thuý Diệp</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:34, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H374" t="n">
+        <v>1</v>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>260104019</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:50:00</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>DT-Nk Sa Đéc</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Như Quỳnh</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11-13, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H375" t="n">
+        <v>3</v>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>260104014</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:26:00</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Nguyễn T Loan</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12-21, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H376" t="n">
+        <v>3</v>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>262703019-1</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:24:00</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Kim Loan</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11-26, - SL: 7)</t>
+        </is>
+      </c>
+      <c r="H377" t="n">
+        <v>7</v>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>260104013</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:22:00</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Tú Loan</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Cùi Giả Zirconia HT (R:22, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H378" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>260104012</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:21:00</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Lưu Quang Đạo</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Cùi Giả Zirconia HT (R:11, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H379" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>262803014-1</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:19:00</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Loan</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:21-22, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H380" t="n">
+        <v>2</v>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>260104011</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:16:00</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Trần Hoài Thu</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:36-45, - SL: 11)</t>
+        </is>
+      </c>
+      <c r="H381" t="n">
+        <v>11</v>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>260104010</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2026-04-01 08:14:00</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>AG-Nk BS Lâm</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:14-16, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H382" t="n">
+        <v>3</v>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>HT</t>
         </is>
       </c>
     </row>

--- a/Data_thang/Thang_04_2026.xlsx
+++ b/Data_thang/Thang_04_2026.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J382"/>
+  <dimension ref="A1:J415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17854,6 +17854,1521 @@
         <v>3</v>
       </c>
       <c r="I382" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>263003039-1</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:54:00</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Tống Minh Luân</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:43-48, - SL: 6)</t>
+        </is>
+      </c>
+      <c r="H383" t="n">
+        <v>6</v>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Đắp hoàn tất</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>Đã đóng gói chờ giao</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>262303048-4</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:50:00</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Trần V Ngãi</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:18-25, - SL: 13)</t>
+        </is>
+      </c>
+      <c r="H384" t="n">
+        <v>13</v>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Sửa Trực Trân</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>Đã đóng gói chờ giao</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>262503048-2</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:47:00</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Nguyễn T Loan</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:15,23-27, - SL: 6)</t>
+        </is>
+      </c>
+      <c r="H385" t="n">
+        <v>6</v>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Sửa Trường Lân</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>Đã đóng gói chờ giao</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>262703039-2</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:47:00</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Trần Văn Thanh</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:37-45, - SL: 12)</t>
+        </is>
+      </c>
+      <c r="H386" t="n">
+        <v>12</v>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>LTTS
+Đạt</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>Đã đóng gói chờ giao</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>263003040-1</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:41:00</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:00:00</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:00:00</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Kim Quỳnh</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:22-23, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H387" t="n">
+        <v>2</v>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Hoàn tất. GẤP</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>Đã đóng gói chờ giao</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>262903047-2</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:17:00</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:00:00</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:00:00</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>SG-Nk  Anh Khôi</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Chúc (Trúc)</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:15-22,33-36, - SL: 11)</t>
+        </is>
+      </c>
+      <c r="H388" t="n">
+        <v>11</v>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Sửa : Trang Trân
+BOOK GRAB NK TRẢ TIỀN</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>262803021-1</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:47:00</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:00:00</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:00:00</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Cô Hoa (38471)</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Răng sứ Chrome - Cobalt (R:35-37,44, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H389" t="n">
+        <v>4</v>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Sửa Vy Hữu</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>262903029-1</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:21:00</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:00:00</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Anh Trung (47242)</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:34, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H390" t="n">
+        <v>1</v>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Sửa Trang Hữu</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>00703036-1</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:17:00</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:00:00</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Lê Thị Xuyên</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:32-42, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H391" t="n">
+        <v>4</v>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>BHHT CS1
+Vạn Tâm Trọng Nhuần Linh
+Giấy: 10h30 ngày 3/4 c gom</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>260104046</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:08:00</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:00:00</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Huỳnh Thị Kim Loan</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:14-23, - SL: 7)</t>
+        </is>
+      </c>
+      <c r="H392" t="n">
+        <v>7</v>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Hoàn tất - CS1
+Giấy 10h30 ngày 3/4 c gom</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>260104045</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:05:00</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:00:00</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Lê Thanh Tú</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Răng sứ Zir- Diamond (R:25-26, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H393" t="n">
+        <v>2</v>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>HT - CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>260104051</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2026-04-01 15:06:00</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:00:00</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>SG-Nk  Hậu - Bình Chánh</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Chiến</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Răng sứ Zolid (R:12-22, - SL: 4); 
+Răng Tạm (R:12-22, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H394" t="n">
+        <v>8</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>TS 
+Đã tách giấy</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>262703048-2</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:50:00</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:00:00</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>LA-Nk Tố Oanh</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Nguyễn Hải Yến</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Full Sứ Ziconia (R:16, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H395" t="n">
+        <v>1</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>LLHT Trang Trân</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>262903038-1</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2026-04-01 11:33:00</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:00:00</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>AG-Nk Hồng Thọ</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Ngọc Như</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11,21, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H396" t="n">
+        <v>2</v>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Sửa Trang Trân
+ĐÃ HẸN</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>260104023</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:10:00</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>AG-Nk Hiệp Thành</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Cùi giả (R:11,13, - SL: 2); 
+Răng sứ kim loại thường (R:11-13, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H397" t="n">
+        <v>5</v>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>260104028</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:18:00</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>ST-Nk BS Thùy</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Tuyền</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:23,43,44-45,47, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H398" t="n">
+        <v>5</v>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>260104026</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>ST-Nk BS Thùy</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Hoàng Anh</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:11,12,21,22, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H399" t="n">
+        <v>4</v>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>260104033</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:34:00</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>AG-Nk An Châu</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Ngô Thị Kim Tuyết</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:14-15, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H400" t="n">
+        <v>2</v>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>260104032</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:35:00</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>AG-Nk Nguyễn Gia</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Trần Thị Kim Ngọc</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11, - SL: 1); 
+Răng sứ Titanium (R:48, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H401" t="n">
+        <v>2</v>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>260104031</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:33:00</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>AG-Nk Nguyễn Gia</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Hồ Phú Lực</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12-21, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H402" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>263003030-1</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:31:00</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>AG-Nk An Châu</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Hà Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:14-15, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H403" t="n">
+        <v>2</v>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>32109010-1</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:45:00</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Út Nal</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:34, - SL: 1); 
+Răng sứ kim loại thường (R:11, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H404" t="n">
+        <v>2</v>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>LHHT 11: Trí Gấm Trọng Vy Phú
+R34 sửa</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>261903053-1</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:27:00</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Chị Phượng (37095)</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:44-47, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H405" t="n">
+        <v>4</v>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Sửa My Trân</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>262503063-2</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:22:00</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Anh Tuấn (43918)</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:27-28,34-36, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H406" t="n">
+        <v>5</v>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>LLHT Trang Hỷ</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>260104044</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:40:00</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026-04-03 08:00:00</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Chị Mai (47294)</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:35-37, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H407" t="n">
+        <v>3</v>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>ht</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>260104052</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00:00</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2026-04-03 08:00:00</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>SG-Nk  An Dương Vương</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Phan Thị Kim Cương</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:24, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H408" t="n">
+        <v>1</v>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>241106026-3</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2026-04-01 12:47:00</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2026-04-03 09:00:00</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>SG-Nk Như Lạc</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Bác Ngọ</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:16, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H409" t="n">
+        <v>1</v>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Sửa Hồng Trân</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>260104053</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2026-04-01 17:26:00</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2026-04-03 10:00:00</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026-04-03 11:00:00</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>SG-Nk Mỹ Á</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Cô Tú</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:22, - SL: 1); 
+Răng Tạm (R:32-42, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H410" t="n">
+        <v>5</v>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>HT
+Đã tách giấy</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>260104047</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2026-04-01 13:24:00</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2026-04-03 10:00:00</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>LA-Nk Kim Oanh</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Tuyền</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:43-45, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H411" t="n">
+        <v>3</v>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>HT
+ĐÃ HẸN</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>260104055</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:55:00</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2026-04-03 13:00:00</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Cô Anh (46784)</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:44, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H412" t="n">
+        <v>1</v>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>260104050</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:05:00</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Cao Thanh Thuỷ</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:16-24,25-26,17, - SL: 13)</t>
+        </is>
+      </c>
+      <c r="H413" t="n">
+        <v>13</v>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>HT CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>260104049</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-04-01 14:00:00</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Trịnh Thị Ngọc Thuý</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:34-38,33, - SL: 6)</t>
+        </is>
+      </c>
+      <c r="H414" t="n">
+        <v>6</v>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>HT - CS 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>260104054</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-04-01 18:50:00</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Anh Thái (47219)</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:21-22,23,24-27,15,32-42,33-34,35-38, - SL: 19)</t>
+        </is>
+      </c>
+      <c r="H415" t="n">
+        <v>19</v>
+      </c>
+      <c r="I415" t="inlineStr">
         <is>
           <t>HT</t>
         </is>

--- a/Data_thang/Thang_04_2026.xlsx
+++ b/Data_thang/Thang_04_2026.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J415"/>
+  <dimension ref="A1:J476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19369,6 +19369,2765 @@
         <v>19</v>
       </c>
       <c r="I415" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>263103055-1</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:56:00</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2026-04-02 12:00:00</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:00:00</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>SG-Nk  Hậu - Bình Chánh</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Loan</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Máng tẩy mềm 1.0mm (R:HTren,HDuoi, - SL: 1); 
+Răng sứ kim loại thường (R:45-46, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H416" t="n">
+        <v>3</v>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Đắp HT 
+Đã tách giấy</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>260104057</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2026-04-01 19:08:00</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026-04-03 08:00:00</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>SG-Nk Huỳnh Lê</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Hồng Thu (14744)</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:32-33,31-42, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H417" t="n">
+        <v>5</v>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>262703029-1</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:37:00</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>AG-Nk Nguyễn Gia</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Trần Thị Thuý Hằng</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11-12, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H418" t="n">
+        <v>2</v>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Sửa Trang - Lân</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>263003019-1</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:34:00</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>NT-Nk BS Thuận</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Phạm Hải</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Full/ mão kim loại sứ titan (R:48, - SL: 1); 
+Răng sứ Titanium (R:45-47, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H419" t="n">
+        <v>4</v>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Sửa Hồng - Hỷ</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>262603026-1</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:29:00</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>NT-Nk BS Thuận</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Phong</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:11-12, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H420" t="n">
+        <v>2</v>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Sửa Hồng - Tuấn</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>261803018-1</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:50:00</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Nguyễn Linh Phương</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:31-44, - SL: 6)</t>
+        </is>
+      </c>
+      <c r="H421" t="n">
+        <v>6</v>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Sửa (Trang-Hỷ)
+KHÔNG HẸN</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>260204003</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:43:00</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00:00</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Phan Thị Bé Lai</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:34-36, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H422" t="n">
+        <v>3</v>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>HT - GẤP. KHÔNG HẸN</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>262803030-2</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:22:00</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:00:00</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Nguyễn T Hường</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:23-24, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H423" t="n">
+        <v>2</v>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Sửa (Trang-Tuấn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>263103036-1</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:50:00</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:00:00</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Cao T Ren</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:22, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H424" t="n">
+        <v>1</v>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>HT
+GẤP - KHÔNG HẸN</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>263103035-1</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:00:00</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Phan Thị Bé Sáu</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:24-27, - SL: 4); 
+Răng sứ Titanium (R:35-36, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H425" t="n">
+        <v>6</v>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Đắp HT + LTHT 
+GẤP. KHÔNG HẸN</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>260204041</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:34:00</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026-04-03 08:00:00</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>TN-Nk  NHO</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>A. Liêm</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:34, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H426" t="n">
+        <v>1</v>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>263103045-1</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:10:00</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026-04-03 09:00:00</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>SG-Nk  An Dương Vương</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Võ Thị Phượng</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:33-37, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H427" t="n">
+        <v>5</v>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Đắp HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>262603037-2</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:43:00</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2026-04-03 10:00:00</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>LA-Nk Tâm Đức</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Gái</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại  trên khung (R:35-37,45-47, - SL: 6)</t>
+        </is>
+      </c>
+      <c r="H428" t="n">
+        <v>6</v>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>LT - đắp hoàn tất
+Vy - Tuấn</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>262603038-2</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:49:00</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2026-04-03 10:00:00</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>LA-Nk Tâm Đức</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Chính</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:16-26, - SL: 12)</t>
+        </is>
+      </c>
+      <c r="H429" t="n">
+        <v>12</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Sửa KHÔNG HẸN
+Vy - Trân</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>260204059</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:07:00</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>SG-Nk  Hậu - Bình Chánh</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Ngọc Bich</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:26, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H430" t="n">
+        <v>1</v>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>260204007</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:00:00</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>CT-NK Thanh Tú</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Phan T Bích Ngân</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:11,21, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H431" t="n">
+        <v>2</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>260204009</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:03:00</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>AG-Nk Thủy Tùng</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Sithon</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:46, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H432" t="n">
+        <v>1</v>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>260204008</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:58:00</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>AG-Nk Thủy Tùng</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Tân Thanh</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Răng sứ Cercon HT (R:37, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H433" t="n">
+        <v>1</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>260204040</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:32:00</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>AG-Nk Hồng Thọ</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Nguyễn T Thu</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:16,36, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H434" t="n">
+        <v>2</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>260204013</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:09:00</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>TV-Nk Đức Hiền</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Chị Trang</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:43-47, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H435" t="n">
+        <v>5</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>260204011</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:05:00</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>DT-Nk BS Lê Văn Đệ</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Phạm Thị Thu Trang</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11-21, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H436" t="n">
+        <v>2</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>260204017</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:20:00</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>AG-Nk Hoàng Phương</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Diệu</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12-21, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H437" t="n">
+        <v>3</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>260204016</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:18:00</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Quang</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Hằng</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:22-23, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H438" t="n">
+        <v>2</v>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>260204015</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:17:00</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>TV-Nk Đức Hiền</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Cô Trang</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H439" t="n">
+        <v>1</v>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>260204019</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:24:00</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>AG-Nk Hoàng Phương</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:22, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H440" t="n">
+        <v>1</v>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>260204032</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:59:00</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>BL-Nk Bs Quân</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Sơn Thị Bích Thuỷ</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Răng sứ Zir- Diamond (R:43-46, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H441" t="n">
+        <v>4</v>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>262903006-1</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:26:00</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>AG-Nk Thủy Tùng</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Cẩm Thy</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Răng sứ Cercon HT (R:45, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H442" t="n">
+        <v>1</v>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Sửa Vy - ko tên</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>260204026</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:45:00</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>AG-Nk Mai Thư- AP</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Lan</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:15-25, - SL: 10)</t>
+        </is>
+      </c>
+      <c r="H443" t="n">
+        <v>10</v>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>HT
+GỬI SỔ ĐẶT HÀNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>260204025</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:42:00</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>TV-Nk Thuấn Thư</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Trần Ngọc Thuý</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:33,44, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H444" t="n">
+        <v>2</v>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>260204021</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:28:00</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Phú Quốc</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:34-35, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H445" t="n">
+        <v>2</v>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>260204022</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:31:00</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Tuyết</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:43-47, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H446" t="n">
+        <v>5</v>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>260204030</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:54:00</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>NT-Nk BS Thuận</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Nguyễn Quá</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Răng sứ Cercon HT (R:13, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H447" t="n">
+        <v>1</v>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>260204029</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:51:00</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>AG-Nk Nguyễn Gia</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Lê Thị Ngọc Quyên</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:46-47, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H448" t="n">
+        <v>2</v>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>260204028</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:49:00</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>AG-Nk An Châu</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Trần Nhựt Em</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:34-35, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H449" t="n">
+        <v>2</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>251209054-3</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:04:00</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>AG-Nk Hiệp Hùng</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Phạm Thị Tâm</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12-22, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H450" t="n">
+        <v>4</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>BHHT (Phong-Sáng-Sĩ-Vy-Trân)</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>260204014</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:11:00</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>DL-Nk Đức Trọng</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Huy</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:26, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H451" t="n">
+        <v>1</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>260204010</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:15:00</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>DL-Nk Đức Trọng</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Uyên</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Mặt dán sứ (R:12,22, - SL: 2); 
+Veneer sứ Ziconia (Cut Back) (R:11,21, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H452" t="n">
+        <v>4</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>260204012</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:08:00</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>DL-Nk Đức Trọng</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Duy</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:37, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H453" t="n">
+        <v>1</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>260204006</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:53:00</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>KG-Nk Phạm Kiều</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Thuỷ</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại đắp sứ VITA (R:23-25, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H454" t="n">
+        <v>3</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>260204005</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:51:00</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>KG-Nk Phạm Kiều</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Mến</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại đắp sứ VITA (R:21, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H455" t="n">
+        <v>1</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>260204004</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:46:00</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>KG-Nk Phạm Kiều</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Phạm Thị Tưởng</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:43-44, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H456" t="n">
+        <v>2</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>260204039</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:30:00</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>AG-Nk Quốc Huy</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Út Hồng</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:34-35, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H457" t="n">
+        <v>2</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>262503024-1</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:10:00</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>AG-Nk Thanh Bình</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Bích Thuỷ</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Full Sứ Ziconia (R:16-17,26, - SL: 3); 
+Răng sứ Zircornia (R:13-15,24-25, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H458" t="n">
+        <v>8</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>LLHT (Trường-Tuấn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>260204043</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:40:00</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>ST-Nk BS Thùy</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Văn Phúc</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:14-16, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H459" t="n">
+        <v>3</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>260204045</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:43:00</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>ST-Nk BS Thùy</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Cẩm Thuý</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:17,25,27, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H460" t="n">
+        <v>3</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>260204048</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:47:00</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>ST-Nk BS Thùy</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>My Nhiên</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:25, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H461" t="n">
+        <v>1</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>260204047</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:45:00</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>ST-Nk BS Thùy</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Diệu Hiền</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:14, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H462" t="n">
+        <v>1</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>260204002</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:40:00</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Đôi</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:35, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H463" t="n">
+        <v>1</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>260204001</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:37:00</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:30:00</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>BL-NK BS Tăng Suy Nghĩ</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Trương Thị Tiếng</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12,25-27,35-38, - SL: 8)</t>
+        </is>
+      </c>
+      <c r="H464" t="n">
+        <v>8</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>262903043-2</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:13:00</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>2026-04-03 19:00:00</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Hồng Hiếu</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:14-15,25, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H465" t="n">
+        <v>3</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>LTHT (Vy-Tuấn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>260204060</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:09:00</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>2026-04-03 19:00:00</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Võ Thị Thanh Tuyến</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12,34-38,44-45, - SL: 8)</t>
+        </is>
+      </c>
+      <c r="H466" t="n">
+        <v>8</v>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>262603041-1</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:01:00</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2026-04-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>LA-Nk Tâm Đức</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Ngọc Trâm</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:15, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H467" t="n">
+        <v>1</v>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>LTHT
+Trực - Hỷ</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>92005059-04</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:38:00</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:00:00</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Đỗ Thị Hoài Phước</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:12-22, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H468" t="n">
+        <v>4</v>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>BHHT (Kten-Tâm-Tâm-Hân-Diễm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>260204046</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:43:00</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:00:00</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Lê T Mỹ Duyên</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H469" t="n">
+        <v>1</v>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>260204055</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:57:00</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-04-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>LA-Nk Tâm Đức</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Phát</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:27, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H470" t="n">
+        <v>1</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Hoàn tất</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>260204051</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2026-04-02 10:04:00</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:00:00</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Châu T Hồng Thắm</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:24-26, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H471" t="n">
+        <v>3</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>260204050</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:55:00</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:00:00</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Lâm T Phụng</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:31-33, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H472" t="n">
+        <v>3</v>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>242112043-1</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:55:00</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:00:00</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Trần T Loan</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:27, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H473" t="n">
+        <v>1</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>BHHT
+My - Thư</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>260204049</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:52:00</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:00:00</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Trần T Kim Phượng</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:13-14, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H474" t="n">
+        <v>2</v>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>260204044</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2026-04-02 09:40:00</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:00:00</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Thụy</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Nguyễn T  Xuân Mai</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:35-37, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H475" t="n">
+        <v>3</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>260204058</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2026-04-02 11:03:00</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>2026-04-04 15:00:00</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>SG-Nk Như Lạc</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Dư Chiêu Bảo</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Veneer sứ Ziconia (Cut Back) (R:25, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H476" t="n">
+        <v>1</v>
+      </c>
+      <c r="I476" t="inlineStr">
         <is>
           <t>HT</t>
         </is>

--- a/Data_thang/Thang_04_2026.xlsx
+++ b/Data_thang/Thang_04_2026.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J476"/>
+  <dimension ref="A1:J500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22130,6 +22130,1091 @@
       <c r="I476" t="inlineStr">
         <is>
           <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>260204072</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>LA-Nk Tố Oanh</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Nguyễn Lê Quốc Duy</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Full sứ Cercon HT (R:36, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H477" t="n">
+        <v>1</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>260204067</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:23:00</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>DT- Nk BS Nhựt NM</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Ánh Nguyệt</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:12, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H478" t="n">
+        <v>1</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>263003046-1</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:30:00</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Nguyễn Trần Xuân Nhuỵ</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Răng sứ Zir- Diamond (R:31-41,32-33,42-43, - SL: 6)</t>
+        </is>
+      </c>
+      <c r="H479" t="n">
+        <v>6</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Sửa (Hồng-Tuấn)
+GỬI CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>260204064</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:30:00</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Cao Quốc Dương</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Răng sứ Cercon HT (R:33-36, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H480" t="n">
+        <v>4</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>HT - GỬI CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>260204063</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:30:00</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Nguyễn T Hồng Cẩm</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:11-21, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H481" t="n">
+        <v>2</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>HT - GỬI CS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>262803052-2</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:12:00</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2026-04-03 12:00:00</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>LA-Nk Tố Oanh</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Thái Thị Đẹt</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:13-15, - SL: 3); 
+Veneer sứ Titanium (Cut Back) (R:12, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H482" t="n">
+        <v>4</v>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Sửa Trang Tuấn</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>260204075</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:32:00</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>LA-Nk  BS Thu</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Phạm T Kiều Chinh</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:12-21, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H483" t="n">
+        <v>3</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>262803058-1</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Ái</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Mỹ Dung</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:46, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H484" t="n">
+        <v>1</v>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>262903031-2</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:38:00</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2026-04-03 15:00:00</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Anh Chung (47041)</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:35-37, - SL: 3)</t>
+        </is>
+      </c>
+      <c r="H485" t="n">
+        <v>3</v>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Sửa Vy Hữu</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>260204080</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:35:00</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>LA-Nk Khánh Hà</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Hồ Thị Kim Liên</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Full Sứ Ziconia (R:36, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H486" t="n">
+        <v>1</v>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>262703057-4</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:11:00</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Ái</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Cao Thị Hồng Phượng</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:43-47, - SL: 5)</t>
+        </is>
+      </c>
+      <c r="H487" t="n">
+        <v>5</v>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Sửa Trường Trân gửi sổ chỉ định</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>262703057-3</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:15:00</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Ái</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Cao Thị Hồng Phượng</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:24-25, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H488" t="n">
+        <v>2</v>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>LT Thử thô Trường Trân</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>260204076</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:36:00</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2026-04-03 14:00:00</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Cẩm Dung</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Bé Nhi</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:26, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H489" t="n">
+        <v>1</v>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>260204069</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:25:00</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Cô Cương (41654)</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:34, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H490" t="n">
+        <v>1</v>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>262803053-2</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>SG-Nk Việt Xuân</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Thu Huỳnh</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Răng sứ Zircornia (R:17, - SL: 1); 
+Răng sứ Zircornia (R:46, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H491" t="n">
+        <v>2</v>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>R17: sửa
+R46: LTHT VY TRÂN</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>260104041-1</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:22:00</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Chú Cửu (47284)</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:38, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H492" t="n">
+        <v>1</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>260204068</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2026-04-02 14:41:00</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>2026-04-03 19:00:00</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>BT-Nk Bác Sĩ Hiếu</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Nguyễn Cao Thái Long</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:46, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H493" t="n">
+        <v>1</v>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>260204074</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>2026-04-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:00:00</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>SG-Nk Việt Xuân</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Lữ Thị Hồng Oanh</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:43, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H494" t="n">
+        <v>1</v>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>260204071</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:26:00</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>2026-04-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>SG-Nk  Anh Khôi</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Phương</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:37, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H495" t="n">
+        <v>1</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>260204070</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:24:00</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2026-04-04 13:00:00</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Hiền (47319)</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Răng sứ Chrome - Cobalt (R:36, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H496" t="n">
+        <v>1</v>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>260204078</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2026-04-02 19:25:00</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2026-04-04 13:00:00</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>SG-Nk Hải Nguyên</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Thầy Thanh (47296)</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Răng sứ Titanium (R:36,45-47, - SL: 4)</t>
+        </is>
+      </c>
+      <c r="H497" t="n">
+        <v>4</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>260204062</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:30:00</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:00:00</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Lê Văn Thanh</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Răng sứ kim loại thường (R:35-36, - SL: 2)</t>
+        </is>
+      </c>
+      <c r="H498" t="n">
+        <v>2</v>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>HT - GỬI CS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>251011044-2</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>2026-04-02 13:00:00</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:00:00</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Huý</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Võ Chí Cường</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>Răng sứ Zir- Diamond (R:15-17,11,21,22,23-26, - SL: 10)</t>
+        </is>
+      </c>
+      <c r="H499" t="n">
+        <v>10</v>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>BHHT (Vạn-Nha Việt x2-Hồng-Tuấn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>262503058-1</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:30:00</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2026-04-04 14:00:00</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2026-04-04 16:00:00</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>LA-Nk BS Cẩm Dung</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Chị Thuý</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Inlay/Onlay/Overlay  kim loại thường (R:17, - SL: 1); 
+Răng sứ Zircornia (R:24, - SL: 1)</t>
+        </is>
+      </c>
+      <c r="H500" t="n">
+        <v>2</v>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>HT ĐÃ HẸN</t>
         </is>
       </c>
     </row>
